--- a/artfynd/A 65041-2019 artfynd.xlsx
+++ b/artfynd/A 65041-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65041-2019 artfynd.xlsx
+++ b/artfynd/A 65041-2019 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>102591570</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593889.0734669575</v>
+        <v>593889</v>
       </c>
       <c r="R3" t="n">
-        <v>6978770.197409366</v>
+        <v>6978771</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 65041-2019 artfynd.xlsx
+++ b/artfynd/A 65041-2019 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>102591570</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 65041-2019 artfynd.xlsx
+++ b/artfynd/A 65041-2019 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>102591570</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 65041-2019 artfynd.xlsx
+++ b/artfynd/A 65041-2019 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>102591570</v>
       </c>
       <c r="B3" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
